--- a/chapters/02/core/AIHE-A03/supp/AIHE-A/xlsx/AIHE-A_workbook.xlsx
+++ b/chapters/02/core/AIHE-A03/supp/AIHE-A/xlsx/AIHE-A_workbook.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R12d108ecfe434f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1T1_Main_Blank" sheetId="2" r:id="R7cecaa62035c4144"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1T1_Main_Worked" sheetId="3" r:id="R0ad453e253b94781"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rdbf66d0417ed4080"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1T1_Main_Blank" sheetId="2" r:id="R84158145e5a84702"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1T1_Main_Worked" sheetId="3" r:id="R627fdb43f06f40e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -480,10 +480,8 @@
           <x:t xml:space="preserve">Related chapters</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapters 4, 5, 12, and 15</x:t>
-        </x:is>
+      <x:c r="B6" s="17" t="str">
+        <x:v>Chapters 2, 4, 9, and 12</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
